--- a/ModifyCCDiffCardTypes.xlsx
+++ b/ModifyCCDiffCardTypes.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <mc:AlternateContent>
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SoapData\"/>
     </mc:Choice>
@@ -18,7 +18,7 @@
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+    <ext uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="139" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="51">
   <si>
     <t>Card Type</t>
   </si>
@@ -178,12 +178,25 @@
   </si>
   <si>
     <t>02/16/2024 23:30:23</t>
+  </si>
+  <si>
+    <t>04/27/2025 17:03:04</t>
+  </si>
+  <si>
+    <t>04/27/2025 17:03:05</t>
+  </si>
+  <si>
+    <t>04/27/2025 17:03:06</t>
+  </si>
+  <si>
+    <t>04/27/2025 17:03:07</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="0"/>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -533,20 +546,20 @@
   <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="9.7109375" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="2" max="2" width="17.28515625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="3" max="3" width="5.85546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="4" max="4" width="5.140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="5" max="5" width="10" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="6" max="6" width="9.28515625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="7" max="7" width="18.140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="8" max="8" width="14.140625" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="9" max="9" width="12.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="10" max="10" width="16.5703125" style="1" customWidth="1" collapsed="1"/>
-    <col min="11" max="11" width="12.85546875" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="12" max="12" width="13.42578125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="13" max="13" width="18.5703125" style="1" bestFit="1" customWidth="1" collapsed="1"/>
-    <col min="14" max="16384" width="9.140625" style="1" collapsed="1"/>
+    <col min="1" max="1" bestFit="true" customWidth="true" style="1" width="9.7109375" collapsed="true"/>
+    <col min="2" max="2" bestFit="true" customWidth="true" style="1" width="17.28515625" collapsed="true"/>
+    <col min="3" max="3" bestFit="true" customWidth="true" style="1" width="5.85546875" collapsed="true"/>
+    <col min="4" max="4" bestFit="true" customWidth="true" style="1" width="5.140625" collapsed="true"/>
+    <col min="5" max="5" bestFit="true" customWidth="true" style="1" width="10.0" collapsed="true"/>
+    <col min="6" max="6" bestFit="true" customWidth="true" style="1" width="9.28515625" collapsed="true"/>
+    <col min="7" max="7" bestFit="true" customWidth="true" style="1" width="18.140625" collapsed="true"/>
+    <col min="8" max="8" bestFit="true" customWidth="true" style="1" width="14.140625" collapsed="true"/>
+    <col min="9" max="9" bestFit="true" customWidth="true" style="1" width="12.42578125" collapsed="true"/>
+    <col min="10" max="10" customWidth="true" style="1" width="16.5703125" collapsed="true"/>
+    <col min="11" max="11" bestFit="true" customWidth="true" style="1" width="12.85546875" collapsed="true"/>
+    <col min="12" max="12" bestFit="true" customWidth="true" style="1" width="13.42578125" collapsed="true"/>
+    <col min="13" max="13" bestFit="true" customWidth="true" style="1" width="18.5703125" collapsed="true"/>
+    <col min="14" max="16384" style="1" width="9.140625" collapsed="true"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:15" x14ac:dyDescent="0.25">
@@ -615,25 +628,23 @@
       <c r="H2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="I2" t="s">
-        <v>41</v>
-      </c>
-      <c r="J2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" t="s">
-        <v>42</v>
-      </c>
-      <c r="O2"/>
+      <c r="I2" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="J2" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="L2" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="M2" t="s" s="1">
+        <v>47</v>
+      </c>
+      <c r="N2" s="1"/>
+      <c r="O2" s="1"/>
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -660,25 +671,23 @@
       <c r="H3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I3" t="s">
-        <v>41</v>
-      </c>
-      <c r="J3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" t="s">
-        <v>43</v>
-      </c>
-      <c r="O3"/>
+      <c r="I3" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="J3" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="K3" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="L3" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="M3" t="s" s="1">
+        <v>48</v>
+      </c>
+      <c r="N3" s="1"/>
+      <c r="O3" s="1"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
@@ -705,25 +714,23 @@
       <c r="H4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I4" t="s">
-        <v>41</v>
-      </c>
-      <c r="J4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" t="s">
-        <v>41</v>
-      </c>
-      <c r="N4" t="s">
-        <v>43</v>
-      </c>
-      <c r="O4"/>
+      <c r="I4" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="J4" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="K4" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="L4" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="M4" t="s" s="1">
+        <v>49</v>
+      </c>
+      <c r="N4" s="1"/>
+      <c r="O4" s="1"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
@@ -750,25 +757,23 @@
       <c r="H5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="I5" t="s">
-        <v>41</v>
-      </c>
-      <c r="J5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N5" t="s">
-        <v>44</v>
-      </c>
-      <c r="O5"/>
+      <c r="I5" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="J5" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="K5" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s" s="1">
+        <v>41</v>
+      </c>
+      <c r="M5" t="s" s="1">
+        <v>50</v>
+      </c>
+      <c r="N5" s="1"/>
+      <c r="O5" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -783,7 +788,7 @@
   <dimension ref="A1:N5"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="14" max="14" width="19.85546875" customWidth="1"/>
+    <col min="14" max="14" customWidth="true" width="19.85546875"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" x14ac:dyDescent="0.25">
@@ -858,19 +863,19 @@
       <c r="I2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="J2" t="s">
-        <v>41</v>
-      </c>
-      <c r="K2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" t="s">
-        <v>41</v>
-      </c>
-      <c r="M2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N2" t="s">
+      <c r="J2" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="K2" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="L2" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="M2" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="N2" t="s" s="0">
         <v>45</v>
       </c>
     </row>
@@ -902,19 +907,19 @@
       <c r="I3" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="J3" t="s">
-        <v>41</v>
-      </c>
-      <c r="K3" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" t="s">
-        <v>41</v>
-      </c>
-      <c r="M3" t="s">
-        <v>41</v>
-      </c>
-      <c r="N3" t="s">
+      <c r="J3" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="K3" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="L3" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="N3" t="s" s="0">
         <v>46</v>
       </c>
     </row>
@@ -946,19 +951,19 @@
       <c r="I4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="J4" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" t="s">
-        <v>41</v>
-      </c>
-      <c r="L4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M4" t="s">
-        <v>41</v>
-      </c>
-      <c r="N4" t="s">
+      <c r="J4" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="K4" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="L4" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="M4" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="N4" t="s" s="0">
         <v>46</v>
       </c>
     </row>
@@ -990,19 +995,19 @@
       <c r="I5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="J5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K5" t="s">
-        <v>41</v>
-      </c>
-      <c r="L5" t="s">
-        <v>41</v>
-      </c>
-      <c r="M5" t="s">
-        <v>41</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="J5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="K5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="L5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="M5" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="N5" t="s" s="0">
         <v>46</v>
       </c>
     </row>
